--- a/shared/vista_seguimiento_pueblo.xlsx
+++ b/shared/vista_seguimiento_pueblo.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MULTA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACUERDOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONVENIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONVENIO_HISTORIAL" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +55,18 @@
       <color rgb="FF78350F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1E3A8A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1E3A8A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +98,21 @@
         <fgColor rgb="FFFDE68A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFDBFE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -100,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,6 +147,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6484,7 +6519,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>JAVIER MELGAREJO CASTILLO</t>
+          <t>JUAN ALEXANDER MELGAREJO MENDEZ</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -13288,7 +13323,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>JAVIER MELGAREJO CASTILLO</t>
+          <t>JUAN ALEXANDER MELGAREJO MENDEZ</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -15500,7 +15535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15572,13 +15607,13 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -15624,13 +15659,13 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15650,13 +15685,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -15676,13 +15711,13 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -15728,13 +15763,13 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15802,13 +15837,13 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -15854,13 +15889,13 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -15906,13 +15941,13 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -15984,13 +16019,13 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16010,13 +16045,13 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -16036,13 +16071,13 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -16062,13 +16097,13 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -16088,13 +16123,13 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -16114,13 +16149,13 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16140,13 +16175,13 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -16188,13 +16223,13 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16214,13 +16249,13 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -16240,13 +16275,13 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -16292,13 +16327,13 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -16318,13 +16353,13 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -16344,13 +16379,13 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -16370,13 +16405,13 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
@@ -16396,13 +16431,13 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
@@ -16422,13 +16457,13 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -16448,13 +16483,13 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -16474,13 +16509,13 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -16500,13 +16535,13 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -16526,13 +16561,13 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -16548,13 +16583,13 @@
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -16600,13 +16635,13 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -16626,13 +16661,13 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -16652,13 +16687,13 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -16678,13 +16713,13 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -16704,13 +16739,13 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -16730,13 +16765,13 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -16782,13 +16817,13 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -16808,13 +16843,13 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
@@ -16860,13 +16895,13 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -16886,13 +16921,13 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -16912,13 +16947,13 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -16938,13 +16973,13 @@
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -17016,13 +17051,13 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -17042,13 +17077,13 @@
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>23</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
@@ -17068,13 +17103,13 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
@@ -17094,13 +17129,13 @@
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -17146,13 +17181,13 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -17172,13 +17207,13 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -17224,13 +17259,13 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
@@ -17276,13 +17311,13 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -17302,13 +17337,13 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -17328,13 +17363,13 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -17354,13 +17389,13 @@
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
@@ -17380,13 +17415,13 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -17406,13 +17441,13 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -17432,13 +17467,13 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -17458,13 +17493,13 @@
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -17510,13 +17545,13 @@
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E78" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -17588,13 +17623,13 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -17614,13 +17649,13 @@
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -17666,13 +17701,13 @@
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -17692,13 +17727,13 @@
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -17718,13 +17753,13 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -17744,13 +17779,13 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -17770,13 +17805,13 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89">
@@ -17796,13 +17831,13 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -17822,13 +17857,13 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
@@ -17848,13 +17883,13 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -17874,13 +17909,13 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -17926,13 +17961,13 @@
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95">
@@ -17952,13 +17987,13 @@
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96">
@@ -17978,13 +18013,13 @@
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -18004,13 +18039,13 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -18030,13 +18065,13 @@
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -18056,13 +18091,13 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -18082,13 +18117,13 @@
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -18108,13 +18143,13 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -18160,13 +18195,13 @@
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E103" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -18186,13 +18221,13 @@
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -18212,13 +18247,13 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -18238,13 +18273,13 @@
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
@@ -18264,13 +18299,13 @@
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
@@ -18316,13 +18351,13 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110">
@@ -18342,13 +18377,13 @@
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E110" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111">
@@ -18368,13 +18403,13 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112">
@@ -18394,13 +18429,13 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E112" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -18420,35 +18455,39 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="E113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>ALVINA CALVO GIRALDO</t>
+        </is>
+      </c>
       <c r="D114" s="5" t="n">
-        <v>1334</v>
+        <v>25</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>1334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -18459,22 +18498,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>ALVINA CALVO GIRALDO</t>
+          <t>CATALINA DURAND DOMINGUEZ</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -18485,22 +18524,22 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>CATALINA DURAND DOMINGUEZ</t>
+          <t>DONATA SAMARITANO CERNA</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -18511,22 +18550,22 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>DONATA SAMARITANO CERNA</t>
+          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -18537,12 +18576,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
+          <t>TERESA LOPEZ SAMARITANO</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
@@ -18563,22 +18602,22 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>TERESA LOPEZ SAMARITANO</t>
+          <t>FELICITA ROSALES PABLO</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E119" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -18589,22 +18628,22 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>FELICITA ROSALES PABLO</t>
+          <t>MISAEL HERRERA PRINCIPE</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -18615,22 +18654,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>MISAEL HERRERA PRINCIPE</t>
+          <t>VIVIANA PROLEON CORREA</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -18641,22 +18680,22 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>VIVIANA PROLEON CORREA</t>
+          <t>EDGAR ROLLY ROSARIO ESPINOZA</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123">
@@ -18667,22 +18706,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>EDGAR ROLLY ROSARIO ESPINOZA</t>
+          <t>MARIA RAMIREZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
         <v>50</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124">
@@ -18693,22 +18732,22 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>MARIA RAMIREZ RODRIGUEZ</t>
+          <t>REYNALDO MEDRANO BORDA</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
@@ -18719,48 +18758,48 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>REYNALDO MEDRANO BORDA</t>
+          <t>RAUL BLAS QUISPE</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>RAUL BLAS QUISPE</t>
+          <t>VICTOR SOLORZANO ROSALES</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127">
@@ -18771,22 +18810,22 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>VICTOR SOLORZANO ROSALES</t>
+          <t>JUDITH VENTURO ROSALES</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
         <v>75</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128">
@@ -18797,22 +18836,22 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>JUDITH VENTURO ROSALES</t>
+          <t>BENITA MARGARITA TAHUA OROPEZA</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -18823,22 +18862,22 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>BENITA MARGARITA TAHUA OROPEZA</t>
+          <t>ALFREDO MONTALVO COSME</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
         <v>25</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -18849,48 +18888,48 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>ALFREDO MONTALVO COSME</t>
+          <t>EUSEBIO CAURINO PEÑA</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>EUSEBIO CAURINO PEÑA</t>
+          <t>CLEMENTE CANTO PATALA</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132">
@@ -18901,74 +18940,74 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>CLEMENTE CANTO PATALA</t>
+          <t>MARIA MARTINA PEÑA VEGA</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E132" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>MARIA MARTINA PEÑA VEGA</t>
+          <t>JESSICA OLIVO INGARUCA</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>JESSICA OLIVO INGARUCA</t>
+          <t>VANESSA MILLA CRUZ</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
         <v>50</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135">
@@ -18979,45 +19018,45 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>VANESSA MILLA CRUZ</t>
+          <t>LUIS ROMERO QUISPE</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>LUIS ROMERO QUISPE</t>
+          <t>PEDRO CANDACHO HUARAC</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F136" s="7" t="n">
         <v>50</v>
@@ -19031,12 +19070,12 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>PEDRO CANDACHO HUARAC</t>
+          <t>ROBERTO PALMADERA MILLA</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -19057,48 +19096,48 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>ROBERTO PALMADERA MILLA</t>
+          <t>MIGUEL MELENDEZ JULCA</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>MIGUEL MELENDEZ JULCA</t>
+          <t>JULIO CHAVARRIA GARCIA</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E139" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140">
@@ -19109,22 +19148,22 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>JULIO CHAVARRIA GARCIA</t>
+          <t>VICKI MASIAS CUSIHUAMAN</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E140" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -19135,22 +19174,22 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>VICKI MASIAS CUSIHUAMAN</t>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -19161,47 +19200,21 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>RENATO ALBORNOS SIGUEÑAS</t>
+          <t>LUZ MERCEDES VARGAS CAURINO</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E142" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>LUZ MERCEDES VARGAS CAURINO</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E143" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -19212,4 +19225,6892 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L156"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Predio</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cuotas antes del ledger (snapshot génesis)</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Pagos en el ledger (jun-2026 →) y saldo vigente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>DEUDA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>DIC-25</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ENE-26</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>FEB-26</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>MAR-26</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ABR-26</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>MAY-26</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>PAGO JUN-26</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>SALDO ACTUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>MARCELINA OBREGON DE AVILA</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>YOLANDA ESPINOZA JAIMES</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>JULIA AGAMA CUZCO</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ESTEBAN REYES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR MELGAREJO CORCINO</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BACILIO UTRILLA FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ELVIRA PASCUALA MINAYA TAHUA</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TEOFILO BRUNO RAMOS DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ESTEBAN REYNALDO ROSALES</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>POMPEYO CELESTINO LLIUYA</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ROSA VICTORIA MILLA MORALES</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>LIRIA PARIAMACHI DE PAZ</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ROSALINA OLIMPIA CIRIACO SOTELO</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ODILON CERNA ROMERO</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>IRMA HUAÑAHUI LOPEZ</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>JUAN RIOS BLAS</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>MARTHA MASIAS CASIHUAMAN DE TERAN</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>MARCELINO VALLADARES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ANTONIO VALLADARES DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>OLGA FLORENTINA HUERTA AGAMA</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>EUSEBIO REYES VILLAFANA</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ALFREDO CARLOS VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>JULIO HUERTA MILLA</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>OSTIN AGÜERO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>FAUSTA HUERTA AGAMA</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>TIMOTEO ROMERO JULCA</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>AGAPITO PRINCIPE SALINAS</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR LOPEZ TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>JUAN VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>ESTEBAN GUERRERO CHINGEL</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>FELIPE DOMINGO VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>ANTONIO CASTILLEJO CUEVA</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>HERMELINDA JARA TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>SANTA ANTONIA SAENZ TICLIO</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TEOFILA FERNANDEZ REYES</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>DARIO ROSALES TICLIO</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>GREGORIO TRUJILLO LEON</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>MARIA NANCY SIGUEÑAS UGARTE</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>DARIO OCTAVIO VEGA JULCA</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>RODRIGO PODESTA ROSAS</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ABIGAIL SONIA GASPAR VEGA</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>ALBERTO TARAZONA CALDAS</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR LAURENCIO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>GUDELIA ELIZABETH MIRANDA VEGA</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>ROSA LUCIA CORONADO LUNA</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>JUAN BAUTISTA PEREZ</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>ELEUTERIO OCAÑA ROMERO</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>ERNESTINA VALLADARES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>REYNALDO MELGAREJO VILCARINO</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L51" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>MARGARITA GOMEZ BONIFACIO</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>CRISOSTOMO ALBORNOZ TICLIO</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SIGUENAS SAENZ</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>BENITA LEON JARA</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L55" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>AUGUSTO ROMERO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>SANTOS BAUTISTA CAPCHA</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L57" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>ANA ROMERO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L58" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>RAQUEL MABEL AVILA MORALES</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L59" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>NATALIA CHINCHAY COLLAS</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR MANUEL JARA ESPINOZA</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L61" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>JHON SAMARITANO HEREDIA</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L62" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>ORLANDO EVARISTO COCHACHIN</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L63" s="10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>JULIO MAYO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>ALEJANDRO LOPEZ ZORRILLA</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>GODOFREDO VASQUEZ LOAYSA</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>JULIO NIETO ORTIZ</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>FRANCISCO MORENO VARA</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>ANSELMO BELVEDER NUÑEZ</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>ROMAN LOZANO MINAYA</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>ALVINO CASTILLEJO VENTURO</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>PEDRO PALMADERA HERRERA</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>ALEJANDRO GASPAR OLORTEGUI</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L73" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>CLEMENTE RODRIGUEZ ROJAS</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L74" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>LOLA MAURICIA ZORRILLA MEDINA</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>DOMINGA CHACARA LOPEZ</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>VALENTIN DURAND VALLADARES</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>JULIO SOLORZANO ESTRADA</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>ROBERTO NIETO HUERTA</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>TEREZA ROMERO BAZAN</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L80" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>ADOLFO ROSARIO ROJAS</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>JULIA BARRERA GARCILAZO</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L82" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>ROSA CARDENAS ALVARADO</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>COMEDOR POPULAR CLUB DE MADRES</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>VILMA CELESTINO VILLAFANA</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L85" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>MARCELO CHINCHAY REGALADO</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>ESPERANZA CHINCHAY COLLAS</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L87" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>CAPILLA DEL PUEBLO</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>HAYDEE RIMAC ALBERTO</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L89" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>JULIA VICTORIA ROBLES CASTILLO</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L90" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>FELICIANA LUISA SANCHEZ RAFAEL</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L91" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>PRUDENCIO VALLADARES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L92" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>MARCIAL SANCHEZ ARAOZ</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L93" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>ANTONIO ESPINOZA SIFUENTES</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L94" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>EMILIA CRUZ OLORTEGUI</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR JOSE ORTEGA DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L96" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR TEODORO FLORES DURAND</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>FORTUNATO VARGAS CABELLO</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>LUISA ELENA CASPA DIAS</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>ELOY ALBERTO SIGUEÑAS UGARTE</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>JAIME VILLANUEVA ALEGRIA</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>DONATA SAMARITANO CERNA</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L102" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>JOSE SOCOLA RUIZ</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L103" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>ALEJANDRO JULCA COLLANTES</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L104" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>EDGAR SILVA GHIGGO</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L105" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>DELIA DORIS HUAMANSUPA PEREZ</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>RAUL OLIVO CORDOVA</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>ELEUTERIO PASTOR LEYVA</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L108" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>MARGARITA SAAVEDRA TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>ANA RODRIGUEZ DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L110" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>LEONCIO CASTILLEJO CAPCHA</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>MAGDA MARIA BLAS MORALES</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>ROGELIO ROSALES CUYA</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>ANDRES QUITO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>JOSE SOLORZANO ESTRADA</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>CARLOS PEREZ RAMIRES</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>CIRILA QUIJANO MELGAREJO</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L117" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>SILVA DEMETRIO BLAS QUISPE</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>JUANA MAYO SALES</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>SEGUNDO SHUMA COMAPA</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H120" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L120" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>RAMON ROSALES MENACHO</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>MATEO ALEJANDRO CACHA SANTOS</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L122" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>ANGELICA TOLENTINO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="10" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>ALVINA CALVO GIRALDO</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L124" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>CATALINA DURAND DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>PEDRO MENDOZA MARQUINA</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H126" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>DONATA SAMARITANO CERNA</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L127" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G128" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L128" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>TERESA LOPEZ SAMARITANO</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G129" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L129" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>REYNA HUERTA MILLA</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G130" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>FELICITA ROSALES PABLO</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G131" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I131" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L131" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>MISAEL HERRERA PRINCIPE</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H132" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L132" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>VIVIANA PROLEON CORREA</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G133" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>MANUEL SAAVEDRA TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G134" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H134" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>EDGAR ROLLY ROSARIO ESPINOZA</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G135" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H135" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I135" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>MARIA RAMIREZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G136" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L136" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>REYNALDO MEDRANO BORDA</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E137" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G137" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H137" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I137" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>RAUL BLAS QUISPE</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G138" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H138" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I138" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L138" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR SOLORZANO ROSALES</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G139" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H139" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I139" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="10" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>JUDITH VENTURO ROSALES</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G140" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H140" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L140" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>BENITA MARGARITA TAHUA OROPEZA</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E141" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G141" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H141" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I141" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>LEONCIO BLAS QUISPE</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G142" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>ALFREDO MONTALVO COSME</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E143" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G143" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L143" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>EUSEBIO CAURINO PEÑA</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G144" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H144" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="10" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>CLEMENTE CANTO PATALA</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E145" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G145" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I145" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>MARIA MARTINA PEÑA VEGA</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G146" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>JESSICA OLIVO INGARUCA</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E147" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G147" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H147" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I147" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L147" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>VANESSA MILLA CRUZ</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G148" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H148" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>LUIS ROMERO QUISPE</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G149" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H149" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L149" s="10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>PEDRO CANDACHO HUARAC</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G150" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H150" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I150" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>ROBERTO PALMADERA MILLA</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E151" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G151" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H151" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>MIGUEL MELENDEZ JULCA</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F152" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G152" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H152" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L152" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>JULIO CHAVARRIA GARCIA</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E153" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H153" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L153" s="10" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>VICKI MASIAS CUSIHUAMAN</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G154" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H154" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I154" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L154" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G155" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>LUZ MERCEDES VARGAS CAURINO</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v/>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G156" s="6" t="n">
+        <v/>
+      </c>
+      <c r="H156" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="D1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/shared/vista_seguimiento_pueblo.xlsx
+++ b/shared/vista_seguimiento_pueblo.xlsx
@@ -5369,14 +5369,20 @@
       <c r="F122" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G122" s="10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H122" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I122" s="11" t="n">
-        <v>48</v>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -6154,13 +6160,13 @@
         <v>50</v>
       </c>
       <c r="G142" s="10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H142" s="7" t="n">
         <v>25</v>
       </c>
       <c r="I142" s="11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="143">
@@ -7511,14 +7517,20 @@
       <c r="F176" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G176" s="10" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H176" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="I176" s="11" t="n">
-        <v>-18</v>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -7862,20 +7874,14 @@
       <c r="F185" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G185" s="10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -8804,14 +8810,20 @@
       <c r="F209" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G209" s="10" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H209" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I209" s="11" t="n">
-        <v>34</v>
+      <c r="G209" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H209" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I209" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -9647,20 +9659,14 @@
       <c r="F230" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G230" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H230" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I230" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G230" s="10" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H230" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -13404,7 +13410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I279"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14332,14 +14338,20 @@
       <c r="F24" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>-25</v>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -14917,14 +14929,20 @@
       <c r="F39" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>-25</v>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -16397,14 +16415,20 @@
       <c r="F77" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I77" s="11" t="n">
-        <v>0</v>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -16476,13 +16500,13 @@
         </is>
       </c>
       <c r="G79" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -16493,37 +16517,37 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>FELIX VELASQUEZ LOPEZ</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>JUAN SAAVEDRA SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="81">
@@ -16534,22 +16558,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>FAUSTINO POMA PALLACA</t>
+          <t>FELIX VELASQUEZ LOPEZ</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
@@ -16575,22 +16599,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>MARIA NANCY SIGUEÑAS UGARTE</t>
+          <t>FAUSTINO POMA PALLACA</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
@@ -16611,27 +16635,27 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>RENEE MEDRANO MALLMA</t>
+          <t>MARIA NANCY SIGUEÑAS UGARTE</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
@@ -16657,31 +16681,37 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>KAREN JAIMES TRUJILLO</t>
+          <t>RENEE MEDRANO MALLMA</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="I84" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -16692,78 +16722,72 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>SONIA ÑAÑAC</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>KAREN JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>59</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>HERMINIO LUCERO TRUJILLO</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="n">
+          <t>SONIA ÑAÑAC</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E86" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H86" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="87">
@@ -16774,31 +16798,37 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>JANETH CHAVEZ CASTILLEJO</t>
+          <t>HERMINIO LUCERO TRUJILLO</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="G87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="I87" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -16809,37 +16839,31 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>DARIO OCTAVIO VEGA JULCA</t>
+          <t>JANETH CHAVEZ CASTILLEJO</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -16850,22 +16874,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>MELQUIADES SULCA HUAMANI</t>
+          <t>DARIO OCTAVIO VEGA JULCA</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
@@ -16891,22 +16915,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>CAMILA DELGADO VEGA</t>
+          <t>MELQUIADES SULCA HUAMANI</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
@@ -16932,12 +16956,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>ABIGAIL SONIA GASPAR VEGA</t>
+          <t>CAMILA DELGADO VEGA</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
@@ -16973,22 +16997,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>TOLENTINO JULCA MORENO</t>
+          <t>ABIGAIL SONIA GASPAR VEGA</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
@@ -17014,22 +17038,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>ALBERTO TARAZONA CALDAS</t>
+          <t>TOLENTINO JULCA MORENO</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
@@ -17055,22 +17079,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>VICTOR LAURENCIO VALLADARES</t>
+          <t>ALBERTO TARAZONA CALDAS</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
@@ -17091,42 +17115,42 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>MARIA ELIZABETH SILVA SOSA</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H95" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="11" t="n">
-        <v>75</v>
+          <t>VICTOR LAURENCIO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -17137,12 +17161,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>ESTELA FLORES LOAYZA</t>
+          <t>MARIA ELIZABETH SILVA SOSA</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -17178,31 +17202,37 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>ANI CRUZ DOMINGUEZ</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="n">
+          <t>ESTELA FLORES LOAYZA</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E97" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F97" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G97" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="H97" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I97" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
@@ -17213,37 +17243,31 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>RUTH LURDINA MILLA CRUZ</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ANI CRUZ DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I98" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -17254,31 +17278,37 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>SANTA ANGELICA VALLLADARES DOMINGUEZ</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <v>50</v>
+          <t>RUTH LURDINA MILLA CRUZ</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G99" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I99" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100">
@@ -17289,28 +17319,28 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>CESAR ALFREDO VIRU GASPAR</t>
+          <t>SANTA ANGELICA VALLLADARES DOMINGUEZ</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I100" s="11" t="n">
         <v>0</v>
@@ -17319,42 +17349,36 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>WILDA CLEOFE ROMERO VALLADARES</t>
+          <t>CESAR ALFREDO VIRU GASPAR</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -17365,22 +17389,22 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>ERNESTINA VALLADARES TRUJILLO</t>
+          <t>WILDA CLEOFE ROMERO VALLADARES</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
@@ -17406,31 +17430,37 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>MARGARITA GOMEZ BONIFACIO</t>
+          <t>ERNESTINA VALLADARES TRUJILLO</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G103" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="I103" s="11" t="n">
-        <v>21</v>
+        <v>50</v>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -17441,37 +17471,31 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>BERNARDO AGUILAR HUAMAN</t>
+          <t>MARGARITA GOMEZ BONIFACIO</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="F104" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="105">
@@ -17482,22 +17506,22 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>16A</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>MARITZA ALBORNOZ SIGUEÑAS</t>
+          <t>BERNARDO AGUILAR HUAMAN</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
@@ -17523,22 +17547,22 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>16B</t>
+          <t>16A</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>CRESOSTO ALBORNOZ TICLLIO</t>
+          <t>MARITZA ALBORNOZ SIGUEÑAS</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
@@ -17564,12 +17588,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>16C</t>
+          <t>16B</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>ELOY SIGUEÑAS UGARTE</t>
+          <t>CRESOSTO ALBORNOZ TICLLIO</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
@@ -17605,22 +17629,22 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16C</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SIGUENAS SAENZ</t>
+          <t>ELOY SIGUEÑAS UGARTE</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E108" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
@@ -17646,22 +17670,22 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>SANTOS BAUTISTA CAPCHA</t>
+          <t>CARLOS ALBERTO SIGUENAS SAENZ</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="8" t="n">
         <v>75</v>
-      </c>
-      <c r="F109" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
@@ -17687,12 +17711,12 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>SERAPIO FERNANDO CARRION MENDOZA</t>
+          <t>SANTOS BAUTISTA CAPCHA</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
@@ -17728,19 +17752,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>RAQUEL MABEL AVILA MORALES</t>
+          <t>SERAPIO FERNANDO CARRION MENDOZA</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F111" s="8" t="n">
         <v>0</v>
@@ -17769,22 +17793,22 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>NATALIA CHINCHAY COLLAS</t>
+          <t>RAQUEL MABEL AVILA MORALES</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
@@ -17810,12 +17834,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>COMEDOR POPULAR CENTRO DE MADRES</t>
+          <t>NATALIA CHINCHAY COLLAS</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -17851,22 +17875,22 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL JARA ESPINOZA</t>
+          <t>COMEDOR POPULAR CENTRO DE MADRES</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
@@ -17887,27 +17911,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>ANTONY JAVIER CRUZ SAMARITANO</t>
+          <t>VICTOR MANUEL JARA ESPINOZA</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
@@ -17933,22 +17957,22 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>IESIY BELEN LOPEZ SAMARITANO</t>
+          <t>ANTONY JAVIER CRUZ SAMARITANO</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
@@ -17974,12 +17998,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>MARUJA AMALIA SAMARUTANIO</t>
+          <t>IESIY BELEN LOPEZ SAMARITANO</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
@@ -18015,31 +18039,37 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>FREDY INGA GAMARA</t>
+          <t>MARUJA AMALIA SAMARUTANIO</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G118" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I118" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -18050,37 +18080,31 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>VIKY SALES PROLEON</t>
+          <t>FREDY INGA GAMARA</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I119" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -18091,12 +18115,12 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>ROSSANA SAMARITANO HEREDIA</t>
+          <t>VIKY SALES PROLEON</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
@@ -18132,12 +18156,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>JHON SAMARITANO HEREDIA</t>
+          <t>ROSSANA SAMARITANO HEREDIA</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
@@ -18173,12 +18197,12 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>EUGENIA HERREDIA DE SAMARITANO</t>
+          <t>JHON SAMARITANO HEREDIA</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
@@ -18214,22 +18238,22 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>YONY JOSE SAMARITANO HERREDIA</t>
+          <t>EUGENIA HERREDIA DE SAMARITANO</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
@@ -18255,12 +18279,12 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>JOSE FRANCISCO SAMARITANO HUAPAYA</t>
+          <t>YONY JOSE SAMARITANO HERREDIA</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
@@ -18296,22 +18320,22 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>TANIA SAMARITANO HERREDIA</t>
+          <t>JOSE FRANCISCO SAMARITANO HUAPAYA</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
@@ -18332,36 +18356,42 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>JULIO MAYO TRUJILLO</t>
+          <t>TANIA SAMARITANO HERREDIA</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E126" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G126" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I126" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -18372,28 +18402,28 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>ALEJANDRO LOPEZ ZORRILLA</t>
+          <t>JULIO MAYO TRUJILLO</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G127" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I127" s="11" t="n">
         <v>0</v>
@@ -18407,12 +18437,12 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>GODOFREDO VASQUEZ LOAYSA</t>
+          <t>ALEJANDRO LOPEZ ZORRILLA</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
@@ -18442,31 +18472,31 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>GREGORIO TOLENTINO SANCHEZ</t>
+          <t>GODOFREDO VASQUEZ LOAYSA</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G129" s="10" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I129" s="11" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -18477,22 +18507,22 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>JULIO NIETO ORTIZ</t>
+          <t>GREGORIO TOLENTINO SANCHEZ</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
@@ -18518,22 +18548,22 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>CIPRIANO LOZANO MINAYA</t>
+          <t>JULIO NIETO ORTIZ</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
@@ -18559,31 +18589,37 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>ROMAN LOZANO MINAYA</t>
+          <t>CIPRIANO LOZANO MINAYA</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G132" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="I132" s="11" t="n">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -18594,31 +18630,31 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>BEATRIZ EDITA TAMARA LLANQUE</t>
+          <t>ROMAN LOZANO MINAYA</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G133" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
@@ -18629,37 +18665,31 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>INOCENTA MILLA BOTELLO</t>
+          <t>BEATRIZ EDITA TAMARA LLANQUE</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H134" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I134" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -18670,22 +18700,22 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>CLEMENTE RODRIGUEZ ROJAS</t>
+          <t>INOCENTA MILLA BOTELLO</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
@@ -18706,24 +18736,24 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>FELICIA ZAPATA FLORES</t>
+          <t>CLEMENTE RODRIGUEZ ROJAS</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F136" s="8" t="n">
         <v>0</v>
@@ -18752,37 +18782,37 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>DANTE MEZA MONTALVO</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G137" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H137" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="11" t="n">
-        <v>75</v>
+          <t>FELICIA ZAPATA FLORES</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -18793,12 +18823,12 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>JUAN CARLOS GRACIANO SALES</t>
+          <t>DANTE MEZA MONTALVO</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -18820,10 +18850,10 @@
         <v>75</v>
       </c>
       <c r="H138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="11" t="n">
         <v>75</v>
-      </c>
-      <c r="I138" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -18834,12 +18864,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>PATRICIA TARAZONA CARBAJAL</t>
+          <t>JUAN CARLOS GRACIANO SALES</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -18861,10 +18891,10 @@
         <v>75</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I139" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -18875,31 +18905,37 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>MARLENY SAMARITANO HEREDIA</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="n">
+          <t>PATRICIA TARAZONA CARBAJAL</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E140" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="8" t="n">
+      <c r="H140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="11" t="n">
         <v>75</v>
-      </c>
-      <c r="G140" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I140" s="11" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="141">
@@ -18910,37 +18946,31 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>OSWALDO WALTER OCAÑA CASCA</t>
+          <t>MARLENY SAMARITANO HEREDIA</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I141" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="142">
@@ -18951,12 +18981,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>JORGE ORENCIO MORENO ROSALES</t>
+          <t>OSWALDO WALTER OCAÑA CASCA</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
@@ -18992,37 +19022,37 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>OLINDA ASCURRA CONTRERAS</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G143" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H143" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="I143" s="11" t="n">
-        <v>59</v>
+          <t>JORGE ORENCIO MORENO ROSALES</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -19033,12 +19063,12 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>TITO COSME CASTILLEJO</t>
+          <t>OLINDA ASCURRA CONTRERAS</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -19060,10 +19090,10 @@
         <v>75</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="I144" s="11" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145">
@@ -19074,12 +19104,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>NELSON NOE MONTALVO CANO</t>
+          <t>TITO COSME CASTILLEJO</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
@@ -19101,10 +19131,10 @@
         <v>75</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I145" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -19115,60 +19145,60 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>MARYURI ZAPATA MARTINEZ</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E146" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F146" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>NELSON NOE MONTALVO CANO</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>OTILIA RAMIRES LUCIANO</t>
+          <t>MARYURI ZAPATA MARTINEZ</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E147" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F147" s="8" t="n">
         <v>0</v>
@@ -19197,19 +19227,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>DOMINGA CHACARA LOPEZ</t>
+          <t>OTILIA RAMIRES LUCIANO</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F148" s="8" t="n">
         <v>0</v>
@@ -19238,31 +19268,37 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>VALENTIN DURAND VALLADARES</t>
+          <t>DOMINGA CHACARA LOPEZ</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G149" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I149" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -19273,37 +19309,31 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>ROBERTO NIETO HUERTA</t>
+          <t>VALENTIN DURAND VALLADARES</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E150" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I150" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -19314,22 +19344,22 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>TEREZA ROMERO BAZAN</t>
+          <t>ROBERTO NIETO HUERTA</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="8" t="n">
         <v>75</v>
-      </c>
-      <c r="F151" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
@@ -19355,31 +19385,37 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>ADOLFO ROSARIO ROJAS</t>
+          <t>TEREZA ROMERO BAZAN</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F152" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G152" s="10" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H152" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="I152" s="11" t="n">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -19390,12 +19426,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>RAMOS SATURNINO MENDOZA</t>
+          <t>ADOLFO ROSARIO ROJAS</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -19407,14 +19443,20 @@
       <c r="F153" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I153" s="11" t="n">
-        <v>0</v>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -19425,31 +19467,31 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>AURELIO DE LA CRUZ PEREZ</t>
+          <t>RAMOS SATURNINO MENDOZA</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E154" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F154" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G154" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I154" s="11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -19460,37 +19502,31 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>ROSA CARDENAS ALVARADO</t>
+          <t>AURELIO DE LA CRUZ PEREZ</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E155" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H155" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I155" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="156">
@@ -19501,22 +19537,22 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>JULIA CARDENAS ALVARADO</t>
+          <t>ROSA CARDENAS ALVARADO</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F156" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
@@ -19537,17 +19573,17 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>COMEDOR POPULAR CLUB DE MADRES</t>
+          <t>JULIA CARDENAS ALVARADO</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -19583,12 +19619,12 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>JOSE YOVERA CHERO</t>
+          <t>COMEDOR POPULAR CLUB DE MADRES</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
@@ -19600,20 +19636,14 @@
       <c r="F158" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G158" s="10" t="n">
+        <v>-75</v>
+      </c>
+      <c r="H158" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -19624,12 +19654,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>JORGE BARBOZA AMANTE</t>
+          <t>JOSE YOVERA CHERO</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -19665,12 +19695,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>VICTOR BARBOZA AMANTE</t>
+          <t>JORGE BARBOZA AMANTE</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
@@ -19706,22 +19736,22 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>MARCELO CHINCHAY REGALADO</t>
+          <t>VICTOR BARBOZA AMANTE</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
@@ -19747,72 +19777,72 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>CAPILLA DEL PUEBLO</t>
+          <t>MARCELO CHINCHAY REGALADO</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F162" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G162" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H162" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I162" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>ALEJANDRO LUIS JULCA</t>
+          <t>CAPILLA DEL PUEBLO</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E163" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H163" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G163" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H163" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I163" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="164">
@@ -19823,22 +19853,22 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>RUBEN LUIS GARCILAZO</t>
+          <t>ALEJANDRO LUIS JULCA</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F164" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
@@ -19864,31 +19894,37 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>FABIAN MONTALVO JULCA</t>
+          <t>RUBEN LUIS GARCILAZO</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E165" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G165" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I165" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -19899,63 +19935,57 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>VICTOR TEODORO FLORES DURAND</t>
+          <t>FABIAN MONTALVO JULCA</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F166" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G166" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H166" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G166" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I166" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>LUISA ELENA CASPA DIAS</t>
+          <t>VICTOR TEODORO FLORES DURAND</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E167" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
@@ -19981,31 +20011,37 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>ELOY ALBERTO SIGUEÑAS UGARTE</t>
+          <t>LUISA ELENA CASPA DIAS</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E168" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F168" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G168" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="I168" s="11" t="n">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -20016,31 +20052,31 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>MAXIMA CARRANZA RODRIGUEZ</t>
+          <t>ELOY ALBERTO SIGUEÑAS UGARTE</t>
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G169" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H169" s="7" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I169" s="11" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="170">
@@ -20051,31 +20087,31 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>DELIA DORIS HUAMANSUPA PEREZ</t>
+          <t>MAXIMA CARRANZA RODRIGUEZ</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E170" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G170" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H170" s="7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I170" s="11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -20086,37 +20122,31 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>RAUL OLIVO CORDOVA</t>
+          <t>DELIA DORIS HUAMANSUPA PEREZ</t>
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I171" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="172">
@@ -20127,22 +20157,22 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>ELEUTERIO PASTOR LEYVA</t>
+          <t>RAUL OLIVO CORDOVA</t>
         </is>
       </c>
       <c r="D172" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E172" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F172" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
@@ -20168,22 +20198,22 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>MARIANELA ELIZABET RIVERA VITATE</t>
+          <t>ELEUTERIO PASTOR LEYVA</t>
         </is>
       </c>
       <c r="D173" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E173" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
@@ -20204,27 +20234,27 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>ENMA CRISTINA BLAS QUISPE</t>
+          <t>MARIANELA ELIZABET RIVERA VITATE</t>
         </is>
       </c>
       <c r="D174" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E174" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F174" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
@@ -20250,31 +20280,37 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>ROSA JUANA MINAYA VILLANUEVA DE VASQUEZ</t>
+          <t>ENMA CRISTINA BLAS QUISPE</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E175" s="7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="G175" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="I175" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -20285,37 +20321,31 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>HUGO MANUEL TAFUR LOPEZ</t>
+          <t>ROSA JUANA MINAYA VILLANUEVA DE VASQUEZ</t>
         </is>
       </c>
       <c r="D176" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E176" s="7" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F176" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H176" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="G176" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I176" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
@@ -20326,31 +20356,37 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>ANDRES QUITO RODRIGUEZ</t>
+          <t>HUGO MANUEL TAFUR LOPEZ</t>
         </is>
       </c>
       <c r="D177" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E177" s="7" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G177" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I177" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -20361,37 +20397,31 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>MERCURIO LUNA FLORES</t>
+          <t>ANDRES QUITO RODRIGUEZ</t>
         </is>
       </c>
       <c r="D178" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E178" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F178" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I178" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -20402,12 +20432,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>JUANA MAYO SALES</t>
+          <t>MERCURIO LUNA FLORES</t>
         </is>
       </c>
       <c r="D179" s="6" t="n">
@@ -20443,19 +20473,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>SEGUNDO SHUMA COMAPA</t>
+          <t>JUANA MAYO SALES</t>
         </is>
       </c>
       <c r="D180" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E180" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F180" s="8" t="n">
         <v>0</v>
@@ -20479,36 +20509,42 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>RAMON ROSALES MENACHO</t>
+          <t>SEGUNDO SHUMA COMAPA</t>
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E181" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G181" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I181" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -20519,28 +20555,28 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>ANGELICA TOLENTINO SANCHEZ</t>
+          <t>RAMON ROSALES MENACHO</t>
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E182" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F182" s="8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G182" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H182" s="7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I182" s="11" t="n">
         <v>0</v>
@@ -20554,37 +20590,31 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>LINDA CARMEN AGURTO SANCHEZ</t>
+          <t>ANGELICA TOLENTINO SANCHEZ</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E183" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H183" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I183" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="G183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I183" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -20595,72 +20625,72 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>DAVID JUAREZ TOLEDO</t>
+          <t>LINDA CARMEN AGURTO SANCHEZ</t>
         </is>
       </c>
       <c r="D184" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E184" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F184" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G184" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="I184" s="11" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>ALVINA CALVO GIRALDO</t>
+          <t>DAVID JUAREZ TOLEDO</t>
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E185" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I185" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="I185" s="11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="186">
@@ -20671,22 +20701,22 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>CATALINA DURAND DOMINGUEZ</t>
+          <t>ALVINA CALVO GIRALDO</t>
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E186" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F186" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
@@ -20712,22 +20742,22 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
+          <t>CATALINA DURAND DOMINGUEZ</t>
         </is>
       </c>
       <c r="D187" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E187" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
@@ -20753,12 +20783,12 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>JUAN ALEXANDER MELGAREJO MENDEZ</t>
+          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
         </is>
       </c>
       <c r="D188" s="6" t="n">
@@ -20794,12 +20824,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>DANTE RUBEN MEDRANO MALLMA</t>
+          <t>JUAN ALEXANDER MELGAREJO MENDEZ</t>
         </is>
       </c>
       <c r="D189" s="6" t="n">
@@ -20835,31 +20865,37 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>27A</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>CLARA LORENZA ARQUELIN</t>
+          <t>DANTE RUBEN MEDRANO MALLMA</t>
         </is>
       </c>
       <c r="D190" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E190" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F190" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G190" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I190" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I190" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -20870,37 +20906,31 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>27A</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>MARIA RAMIREZ RODRIGUEZ</t>
+          <t>CLARA LORENZA ARQUELIN</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E191" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H191" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I191" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I191" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -20911,22 +20941,22 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>CARMELO RAMIREZ RODRIGUEZ</t>
+          <t>MARIA RAMIREZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D192" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E192" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F192" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
@@ -20952,66 +20982,72 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>REYNALDO MEDRANO BORDA</t>
+          <t>CARMELO RAMIREZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E193" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G193" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="I193" s="11" t="n">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="G193" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I193" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>VICTOR SOLORZANO ROSALES</t>
+          <t>REYNALDO MEDRANO BORDA</t>
         </is>
       </c>
       <c r="D194" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E194" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F194" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G194" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H194" s="7" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I194" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -21022,37 +21058,31 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>JUDITH VENTURO ROSALES</t>
+          <t>VICTOR SOLORZANO ROSALES</t>
         </is>
       </c>
       <c r="D195" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E195" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H195" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I195" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I195" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -21063,31 +21093,37 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>BENITA MARGARITA TAHUA OROPEZA</t>
+          <t>JUDITH VENTURO ROSALES</t>
         </is>
       </c>
       <c r="D196" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E196" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F196" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G196" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I196" s="11" t="n">
-        <v>44</v>
+        <v>0</v>
+      </c>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I196" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -21098,31 +21134,31 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>JUANA VICTORIA ARMAS HUARCA</t>
+          <t>BENITA MARGARITA TAHUA OROPEZA</t>
         </is>
       </c>
       <c r="D197" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E197" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G197" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H197" s="7" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I197" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198">
@@ -21133,37 +21169,31 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>RUFINA FRANCISCO JIMENEZ</t>
+          <t>JUANA VICTORIA ARMAS HUARCA</t>
         </is>
       </c>
       <c r="D198" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E198" s="7" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F198" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H198" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I198" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G198" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I198" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="199">
@@ -21174,22 +21204,22 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>RAUL ROMERO MAYO</t>
+          <t>RUFINA FRANCISCO JIMENEZ</t>
         </is>
       </c>
       <c r="D199" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E199" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F199" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
@@ -21215,22 +21245,22 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>MAURICIA C. DURAND VALLADARES</t>
+          <t>RAUL ROMERO MAYO</t>
         </is>
       </c>
       <c r="D200" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E200" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F200" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
@@ -21256,19 +21286,19 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>CALIXTO BLAS TRUJILLO</t>
+          <t>MAURICIA C. DURAND VALLADARES</t>
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E201" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F201" s="8" t="n">
         <v>0</v>
@@ -21297,19 +21327,19 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>FLOR VALDIVIA MILLA</t>
+          <t>CALIXTO BLAS TRUJILLO</t>
         </is>
       </c>
       <c r="D202" s="6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E202" s="7" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F202" s="8" t="n">
         <v>0</v>
@@ -21338,31 +21368,37 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>EUSEBIO CAURINO PEÑA</t>
+          <t>FLOR VALDIVIA MILLA</t>
         </is>
       </c>
       <c r="D203" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E203" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F203" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G203" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H203" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I203" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G203" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I203" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -21373,78 +21409,72 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>RAUL BENITO QUISPE BARRERA</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>EUSEBIO CAURINO PEÑA</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E204" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="G204" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H204" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I204" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>JUAN CABELLO ROMERO</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E205" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G205" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H205" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I205" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>RAUL BENITO QUISPE BARRERA</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="206">
@@ -21455,31 +21485,37 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>JUANA MORALES VEGA</t>
+          <t>JUAN CABELLO ROMERO</t>
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E206" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F206" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G206" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H206" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I206" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I206" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -21490,37 +21526,31 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>JUDITH MARGOT LUIS PEÑA</t>
-        </is>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E207" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F207" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>JUANA MORALES VEGA</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E207" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="G207" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H207" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I207" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -21531,12 +21561,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>EMILIANO PANTOJA SOLANO</t>
+          <t>JUDITH MARGOT LUIS PEÑA</t>
         </is>
       </c>
       <c r="D208" s="9" t="inlineStr">
@@ -21572,10 +21602,14 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C209" s="5" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>EMILIANO PANTOJA SOLANO</t>
+        </is>
+      </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -21592,13 +21626,13 @@
         </is>
       </c>
       <c r="G209" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H209" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I209" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="210">
@@ -21609,37 +21643,33 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>PABLO ROMERO GARCILAZO</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E210" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F210" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G210" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H210" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I210" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr"/>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G210" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -21650,27 +21680,37 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C211" s="5" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>PABLO ROMERO GARCILAZO</t>
+        </is>
+      </c>
       <c r="D211" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E211" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F211" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G211" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I211" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I211" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -21681,28 +21721,24 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>CLEMENTE CANTO PATALA</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr"/>
       <c r="D212" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E212" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F212" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G212" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H212" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="I212" s="11" t="n">
         <v>0</v>
@@ -21716,37 +21752,31 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>MARIA MARTINA PEÑA VEGA</t>
+          <t>CLEMENTE CANTO PATALA</t>
         </is>
       </c>
       <c r="D213" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E213" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F213" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H213" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I213" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G213" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I213" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -21757,12 +21787,12 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>VICTOR JUAREZ CORZO</t>
+          <t>MARIA MARTINA PEÑA VEGA</t>
         </is>
       </c>
       <c r="D214" s="6" t="n">
@@ -21793,36 +21823,42 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>IDA HUACANCA CASCA</t>
+          <t>VICTOR JUAREZ CORZO</t>
         </is>
       </c>
       <c r="D215" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E215" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F215" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G215" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I215" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I215" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -21833,37 +21869,31 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>JESSICA OLIVO INGARUCA</t>
+          <t>IDA HUACANCA CASCA</t>
         </is>
       </c>
       <c r="D216" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E216" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F216" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H216" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I216" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G216" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I216" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -21874,31 +21904,37 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>ROSA TOLENTINO SANCHEZ</t>
+          <t>JESSICA OLIVO INGARUCA</t>
         </is>
       </c>
       <c r="D217" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E217" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F217" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G217" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H217" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I217" s="11" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I217" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -21909,31 +21945,31 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>FLORA MARIA CASTILLEJO VENTURO</t>
+          <t>ROSA TOLENTINO SANCHEZ</t>
         </is>
       </c>
       <c r="D218" s="6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E218" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F218" s="8" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="G218" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H218" s="7" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I218" s="11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="219">
@@ -21944,28 +21980,28 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>DONATO ENRIQUE RAMIRES</t>
+          <t>FLORA MARIA CASTILLEJO VENTURO</t>
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E219" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F219" s="8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G219" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H219" s="7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I219" s="11" t="n">
         <v>0</v>
@@ -21974,33 +22010,33 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>WILDER SANTIAGO SANTIAGO</t>
+          <t>DONATO ENRIQUE RAMIRES</t>
         </is>
       </c>
       <c r="D220" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E220" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F220" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G220" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H220" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I220" s="11" t="n">
         <v>0</v>
@@ -22014,37 +22050,31 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>ANA GARRO ROJAS</t>
+          <t>WILDER SANTIAGO SANTIAGO</t>
         </is>
       </c>
       <c r="D221" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E221" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F221" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H221" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I221" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G221" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I221" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -22055,27 +22085,37 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C222" s="5" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>ANA GARRO ROJAS</t>
+        </is>
+      </c>
       <c r="D222" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E222" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F222" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G222" s="10" t="n">
-        <v>-75</v>
-      </c>
-      <c r="H222" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I222" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I222" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -22086,37 +22126,27 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>MIRIAM DIAZ MAMANI</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr"/>
       <c r="D223" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E223" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F223" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G223" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H223" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I223" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G223" s="10" t="n">
+        <v>-75</v>
+      </c>
+      <c r="H223" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -22127,31 +22157,37 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>VALERIO PORFILIO JAVIER SANTIAGO</t>
+          <t>MIRIAM DIAZ MAMANI</t>
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E224" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F224" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G224" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="I224" s="11" t="n">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I224" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -22162,12 +22198,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>VICTORIA COSME CERNA</t>
+          <t>VALERIO PORFILIO JAVIER SANTIAGO</t>
         </is>
       </c>
       <c r="D225" s="6" t="n">
@@ -22179,20 +22215,14 @@
       <c r="F225" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G225" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H225" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I225" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G225" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="I225" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="226">
@@ -22203,12 +22233,12 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>RUBI MORENO COSME</t>
+          <t>VICTORIA COSME CERNA</t>
         </is>
       </c>
       <c r="D226" s="6" t="n">
@@ -22220,14 +22250,20 @@
       <c r="F226" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G226" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H226" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I226" s="11" t="n">
-        <v>0</v>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I226" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -22238,28 +22274,28 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>LUCIA MORENO ROSALES</t>
+          <t>RUBI MORENO COSME</t>
         </is>
       </c>
       <c r="D227" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E227" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F227" s="8" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="G227" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H227" s="7" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="I227" s="11" t="n">
         <v>0</v>
@@ -22268,42 +22304,36 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>MIRO ORLANDO CERNA MELGAREJO</t>
+          <t>LUCIA MORENO ROSALES</t>
         </is>
       </c>
       <c r="D228" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E228" s="7" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F228" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H228" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I228" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="G228" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="I228" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -22314,22 +22344,22 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>SAMUEL SAMARITANO ROMERO</t>
+          <t>MIRO ORLANDO CERNA MELGAREJO</t>
         </is>
       </c>
       <c r="D229" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E229" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F229" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
@@ -22355,22 +22385,22 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>LUISA AURORA SAMARITANO VEGA</t>
+          <t>SAMUEL SAMARITANO ROMERO</t>
         </is>
       </c>
       <c r="D230" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E230" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="8" t="n">
         <v>75</v>
-      </c>
-      <c r="F230" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
@@ -22396,22 +22426,22 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>PEDRO CANDACHO HUARAC</t>
+          <t>LUISA AURORA SAMARITANO VEGA</t>
         </is>
       </c>
       <c r="D231" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E231" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F231" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
@@ -22437,12 +22467,12 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>JUVENAL MENDOZA JULCA</t>
+          <t>PEDRO CANDACHO HUARAC</t>
         </is>
       </c>
       <c r="D232" s="6" t="n">
@@ -22478,22 +22508,22 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>JOSE PALMADERA MILLA</t>
+          <t>JUVENAL MENDOZA JULCA</t>
         </is>
       </c>
       <c r="D233" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E233" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F233" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
@@ -22519,31 +22549,37 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>ROBERTO PALMADERA MILLA</t>
+          <t>JOSE PALMADERA MILLA</t>
         </is>
       </c>
       <c r="D234" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E234" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F234" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G234" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H234" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I234" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I234" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -22554,63 +22590,57 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>YOLANDA RIMAC CULLA</t>
+          <t>ROBERTO PALMADERA MILLA</t>
         </is>
       </c>
       <c r="D235" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E235" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F235" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G235" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H235" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I235" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G235" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I235" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>MARCELINA GOMEZ BONIFACIO</t>
+          <t>YOLANDA RIMAC CULLA</t>
         </is>
       </c>
       <c r="D236" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E236" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F236" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
@@ -22636,12 +22666,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>BENILDA PALACIOS RODRIGUEZ</t>
+          <t>MARCELINA GOMEZ BONIFACIO</t>
         </is>
       </c>
       <c r="D237" s="6" t="n">
@@ -22672,17 +22702,17 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>MIRIAM SIGUEÑAS SAENZ</t>
+          <t>BENILDA PALACIOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="D238" s="6" t="n">
@@ -22718,31 +22748,37 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>JANET VASQUEZ MINAYA</t>
+          <t>MIRIAM SIGUEÑAS SAENZ</t>
         </is>
       </c>
       <c r="D239" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E239" s="7" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F239" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="G239" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="I239" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I239" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -22753,28 +22789,28 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>VIOLETA CAURINO CABELLO</t>
+          <t>JANET VASQUEZ MINAYA</t>
         </is>
       </c>
       <c r="D240" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F240" s="8" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G240" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="7" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="I240" s="11" t="n">
         <v>0</v>
@@ -22788,37 +22824,31 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>RUMALDA MORENO ROSALES</t>
+          <t>VIOLETA CAURINO CABELLO</t>
         </is>
       </c>
       <c r="D241" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E241" s="7" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F241" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H241" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I241" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="G241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I241" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -22829,19 +22859,19 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>CARMEN MELCHOR ALBORNOZ</t>
+          <t>RUMALDA MORENO ROSALES</t>
         </is>
       </c>
       <c r="D242" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E242" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F242" s="8" t="n">
         <v>0</v>
@@ -22865,27 +22895,27 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>JENY JAIMES TRUJILLO</t>
+          <t>CARMEN MELCHOR ALBORNOZ</t>
         </is>
       </c>
       <c r="D243" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E243" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F243" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
@@ -22911,12 +22941,12 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>JOSE LUIS VARGAS CAURINO</t>
+          <t>JENY JAIMES TRUJILLO</t>
         </is>
       </c>
       <c r="D244" s="6" t="n">
@@ -22928,14 +22958,20 @@
       <c r="F244" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G244" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I244" s="11" t="n">
-        <v>50</v>
+      <c r="G244" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H244" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I244" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -22946,31 +22982,31 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>LOURDES SOCOLA ADANAQUE</t>
+          <t>JOSE LUIS VARGAS CAURINO</t>
         </is>
       </c>
       <c r="D245" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E245" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F245" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G245" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H245" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I245" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="246">
@@ -22981,37 +23017,31 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>JULIAN PABLO ROCA VALENCIA</t>
+          <t>LOURDES SOCOLA ADANAQUE</t>
         </is>
       </c>
       <c r="D246" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E246" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F246" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H246" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I246" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G246" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -23022,31 +23052,37 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>ORTENCIA FLAVIA CABRACANCHA CARRERA</t>
+          <t>JULIAN PABLO ROCA VALENCIA</t>
         </is>
       </c>
       <c r="D247" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E247" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F247" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G247" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I247" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H247" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I247" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -23057,37 +23093,31 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>MARIA PASTOR SALES DE CARRASCO</t>
+          <t>ORTENCIA FLAVIA CABRACANCHA CARRERA</t>
         </is>
       </c>
       <c r="D248" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E248" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F248" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G248" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H248" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I248" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G248" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I248" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -23098,22 +23128,22 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>CRISTINA PASTOR SALES DE MORALES</t>
+          <t>MARIA PASTOR SALES DE CARRASCO</t>
         </is>
       </c>
       <c r="D249" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E249" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F249" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G249" s="9" t="inlineStr">
         <is>
@@ -23139,31 +23169,37 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>DEYSI PASTOR SALES</t>
+          <t>CRISTINA PASTOR SALES DE MORALES</t>
         </is>
       </c>
       <c r="D250" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E250" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F250" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G250" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I250" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H250" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I250" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -23174,31 +23210,31 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>RENATO ALBORNOS SIGUEÑAS</t>
+          <t>DEYSI PASTOR SALES</t>
         </is>
       </c>
       <c r="D251" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E251" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F251" s="8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G251" s="10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H251" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I251" s="11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -23209,22 +23245,22 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>YASMINA JAIMES TRUJILLO</t>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
         </is>
       </c>
       <c r="D252" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E252" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F252" s="8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G252" s="9" t="inlineStr">
         <is>
@@ -23245,17 +23281,17 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>MAGNA ABREGO ISIDRO</t>
+          <t>YASMINA JAIMES TRUJILLO</t>
         </is>
       </c>
       <c r="D253" s="6" t="n">
@@ -23267,14 +23303,20 @@
       <c r="F253" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G253" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="I253" s="11" t="n">
-        <v>30</v>
+      <c r="G253" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H253" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I253" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -23285,37 +23327,31 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>CARLOS JARA GOMEZ</t>
+          <t>MAGNA ABREGO ISIDRO</t>
         </is>
       </c>
       <c r="D254" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E254" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F254" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I254" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G254" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I254" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="255">
@@ -23326,12 +23362,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>BERTHA ELVA GASPAR PEÑA</t>
+          <t>CARLOS JARA GOMEZ</t>
         </is>
       </c>
       <c r="D255" s="6" t="n">
@@ -23367,37 +23403,37 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>OLINDA LOPEZ VERDE</t>
-        </is>
-      </c>
-      <c r="D256" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E256" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F256" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G256" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H256" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I256" s="11" t="n">
-        <v>75</v>
+          <t>BERTHA ELVA GASPAR PEÑA</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E256" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F256" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I256" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -23408,12 +23444,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>LUZ OSORIO MELGAREJO</t>
+          <t>OLINDA LOPEZ VERDE</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
@@ -23449,12 +23485,12 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>NENA MELENDEZ JULCA</t>
+          <t>LUZ OSORIO MELGAREJO</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
@@ -23490,37 +23526,37 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>LUCINDA EMMA BLAS</t>
-        </is>
-      </c>
-      <c r="D259" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E259" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F259" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H259" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I259" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>NENA MELENDEZ JULCA</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H259" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="260">
@@ -23531,22 +23567,22 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>GABBY ALICIA HEREDIA ESPINOZA</t>
+          <t>LUCINDA EMMA BLAS</t>
         </is>
       </c>
       <c r="D260" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E260" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F260" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
@@ -23572,22 +23608,22 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>ADRIAN MARCIAL ANTONIO MURGA</t>
+          <t>GABBY ALICIA HEREDIA ESPINOZA</t>
         </is>
       </c>
       <c r="D261" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E261" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F261" s="8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
@@ -23613,22 +23649,22 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>YOLANDA MERCEDES LOZANO MINAYA</t>
+          <t>ADRIAN MARCIAL ANTONIO MURGA</t>
         </is>
       </c>
       <c r="D262" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E262" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F262" s="8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
@@ -23654,22 +23690,22 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>ELVIRA MINAYA LOZANO</t>
+          <t>YOLANDA MERCEDES LOZANO MINAYA</t>
         </is>
       </c>
       <c r="D263" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E263" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="8" t="n">
         <v>75</v>
-      </c>
-      <c r="F263" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
@@ -23690,27 +23726,27 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>EDY SANCHEZ RODRIGUEZ</t>
+          <t>ELVIRA MINAYA LOZANO</t>
         </is>
       </c>
       <c r="D264" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E264" s="7" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F264" s="8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
@@ -23736,22 +23772,22 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>ISENIA YESICA CASTILLO BRONCANO</t>
+          <t>EDY SANCHEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D265" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E265" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F265" s="8" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
@@ -23777,31 +23813,37 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>JUDITH MONTAÑEZ ROJAS</t>
+          <t>ISENIA YESICA CASTILLO BRONCANO</t>
         </is>
       </c>
       <c r="D266" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E266" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F266" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G266" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I266" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -23812,37 +23854,31 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>BELISARIO MORALES HERRERA</t>
+          <t>JUDITH MONTAÑEZ ROJAS</t>
         </is>
       </c>
       <c r="D267" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E267" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F267" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H267" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I267" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G267" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I267" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -23853,72 +23889,72 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>HAYDEE CERNA NEYRA</t>
+          <t>BELISARIO MORALES HERRERA</t>
         </is>
       </c>
       <c r="D268" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E268" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F268" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G268" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I268" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G268" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H268" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I268" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>ESTHEFANY MAGALY PONTE SANCHEZ</t>
+          <t>HAYDEE CERNA NEYRA</t>
         </is>
       </c>
       <c r="D269" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E269" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F269" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G269" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H269" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I269" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G269" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I269" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -23929,22 +23965,22 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>ALEJANDRO GRADOS APELO</t>
+          <t>ESTHEFANY MAGALY PONTE SANCHEZ</t>
         </is>
       </c>
       <c r="D270" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E270" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F270" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
@@ -23970,22 +24006,22 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>MILAGROS SIGUEÑAS SAENZ</t>
+          <t>ALEJANDRO GRADOS APELO</t>
         </is>
       </c>
       <c r="D271" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E271" s="7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F271" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
@@ -24011,31 +24047,37 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>ROSA DURAND SALES</t>
+          <t>MILAGROS SIGUEÑAS SAENZ</t>
         </is>
       </c>
       <c r="D272" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E272" s="7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F272" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G272" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I272" s="11" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I272" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -24046,12 +24088,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>ALFREDO GRADOS APELO</t>
+          <t>ROSA DURAND SALES</t>
         </is>
       </c>
       <c r="D273" s="6" t="n">
@@ -24067,10 +24109,10 @@
         <v>0</v>
       </c>
       <c r="H273" s="7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I273" s="11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -24081,37 +24123,31 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>OSCAR ROGER FLORES TRUJILLO</t>
+          <t>ALFREDO GRADOS APELO</t>
         </is>
       </c>
       <c r="D274" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E274" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F274" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H274" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I274" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G274" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I274" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="275">
@@ -24122,22 +24158,22 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>HERMENIJILDA CONDOR ARTICA</t>
+          <t>OSCAR ROGER FLORES TRUJILLO</t>
         </is>
       </c>
       <c r="D275" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E275" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F275" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
@@ -24163,22 +24199,22 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>JAVIER ESPINOZA FERNANDEZ</t>
+          <t>HERMENIJILDA CONDOR ARTICA</t>
         </is>
       </c>
       <c r="D276" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E276" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F276" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G276" s="9" t="inlineStr">
         <is>
@@ -24204,19 +24240,19 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>MARTHA BACILIO RAMOS</t>
+          <t>JAVIER ESPINOZA FERNANDEZ</t>
         </is>
       </c>
       <c r="D277" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E277" s="7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F277" s="8" t="n">
         <v>0</v>
@@ -24245,19 +24281,19 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>MARIA BACILIO RAMOS</t>
+          <t>MARTHA BACILIO RAMOS</t>
         </is>
       </c>
       <c r="D278" s="6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E278" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F278" s="8" t="n">
         <v>0</v>
@@ -24286,34 +24322,75 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>MARIA BACILIO RAMOS</t>
+        </is>
+      </c>
+      <c r="D279" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E279" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F279" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H279" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I279" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C279" s="5" t="inlineStr">
+      <c r="C280" s="5" t="inlineStr">
         <is>
           <t>WILSON PATRICIO HUAYTA</t>
         </is>
       </c>
-      <c r="D279" s="6" t="n">
+      <c r="D280" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="E279" s="7" t="n">
+      <c r="E280" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="F279" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H279" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I279" s="9" t="inlineStr">
+      <c r="F280" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H280" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I280" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24335,7 +24412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24590,14 +24667,20 @@
       <c r="F7" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>-50</v>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -24785,14 +24868,20 @@
       <c r="F12" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>-50</v>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -24931,14 +25020,20 @@
       <c r="F16" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>-50</v>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -25530,14 +25625,20 @@
       <c r="F31" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>-25</v>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -25799,14 +25900,20 @@
       <c r="F38" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>-21</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>-16</v>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -26749,20 +26856,14 @@
       <c r="F62" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G62" s="10" t="n">
+        <v>-75</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -27369,14 +27470,20 @@
       <c r="F78" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G78" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H78" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I78" s="11" t="n">
-        <v>-25</v>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -27808,14 +27915,20 @@
       <c r="F89" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G89" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H89" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="I89" s="11" t="n">
-        <v>-30</v>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -28124,14 +28237,20 @@
       <c r="F97" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G97" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H97" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I97" s="11" t="n">
-        <v>-25</v>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -28159,14 +28278,20 @@
       <c r="F98" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G98" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H98" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I98" s="11" t="n">
-        <v>-25</v>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -28821,31 +28946,37 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>MAGDA MARIA BLAS MORALES</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="8" t="n">
-        <v>50</v>
+          <t>RAMON REQUEZ MENDOZA</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G115" s="10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I115" s="11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116">
@@ -28856,28 +28987,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>ANDRES QUITO RODRIGUEZ</t>
+          <t>MAGDA MARIA BLAS MORALES</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I116" s="11" t="n">
         <v>0</v>
@@ -28891,28 +29022,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>CARLOS PEREZ RAMIRES</t>
+          <t>ANDRES QUITO RODRIGUEZ</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G117" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I117" s="11" t="n">
         <v>0</v>
@@ -28926,37 +29057,31 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>CIRILA QUIJANO MELGAREJO</t>
+          <t>CARLOS PEREZ RAMIRES</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I118" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -28967,12 +29092,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>SEGUNDO SHUMA COMAPA</t>
+          <t>CIRILA QUIJANO MELGAREJO</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
@@ -29003,36 +29128,42 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>RAMON ROSALES MENACHO</t>
+          <t>SEGUNDO SHUMA COMAPA</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G120" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I120" s="11" t="n">
-        <v>25</v>
+        <v>25</v>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -29043,37 +29174,31 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>MATEO ALEJANDRO CACHA SANTOS</t>
+          <t>RAMON ROSALES MENACHO</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I121" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="122">
@@ -29084,72 +29209,72 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>ANGELICA TOLENTINO SANCHEZ</t>
+          <t>MATEO ALEJANDRO CACHA SANTOS</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="G122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I122" s="11" t="n">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>ALVINA CALVO GIRALDO</t>
+          <t>ANGELICA TOLENTINO SANCHEZ</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="124">
@@ -29160,19 +29285,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>CATALINA DURAND DOMINGUEZ</t>
+          <t>ALVINA CALVO GIRALDO</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>0</v>
@@ -29201,19 +29326,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>DONATA SAMARITANO CERNA</t>
+          <t>CATALINA DURAND DOMINGUEZ</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F125" s="8" t="n">
         <v>0</v>
@@ -29242,12 +29367,12 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
+          <t>DONATA SAMARITANO CERNA</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
@@ -29283,22 +29408,22 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>TERESA LOPEZ SAMARITANO</t>
+          <t>SIMONA GASPAR OLORTEGUI DE MONTALVO</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
@@ -29324,22 +29449,22 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>FELICITA ROSALES PABLO</t>
+          <t>TERESA LOPEZ SAMARITANO</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E128" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
@@ -29365,12 +29490,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>MISAEL HERRERA PRINCIPE</t>
+          <t>FELICITA ROSALES PABLO</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -29406,19 +29531,19 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>VIVIANA PROLEON CORREA</t>
+          <t>MISAEL HERRERA PRINCIPE</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F130" s="8" t="n">
         <v>0</v>
@@ -29447,31 +29572,37 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>EDGAR ROLLY ROSARIO ESPINOZA</t>
+          <t>VIVIANA PROLEON CORREA</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E131" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I131" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -29482,19 +29613,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>MARIA RAMIREZ RODRIGUEZ</t>
+          <t>EDGAR ROLLY ROSARIO ESPINOZA</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>25</v>
@@ -29503,10 +29634,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I132" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
@@ -29517,37 +29648,31 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>REYNALDO MEDRANO BORDA</t>
+          <t>MARIA RAMIREZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F133" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G133" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I133" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -29558,22 +29683,22 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>RAUL BLAS QUISPE</t>
+          <t>REYNALDO MEDRANO BORDA</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
         <v>25</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
@@ -29594,36 +29719,42 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>VICTOR SOLORZANO ROSALES</t>
+          <t>RAUL BLAS QUISPE</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I135" s="11" t="n">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -29634,31 +29765,31 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>JUDITH VENTURO ROSALES</t>
+          <t>VICTOR SOLORZANO ROSALES</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G136" s="10" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>-50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="137">
@@ -29669,22 +29800,22 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>BENITA MARGARITA TAHUA OROPEZA</t>
+          <t>JUDITH VENTURO ROSALES</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
@@ -29710,19 +29841,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>ALFREDO MONTALVO COSME</t>
+          <t>BENITA MARGARITA TAHUA OROPEZA</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -29751,31 +29882,37 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>FLOR VALDIVIA MILLA</t>
+          <t>ALFREDO MONTALVO COSME</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="G139" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="H139" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="I139" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -29786,66 +29923,66 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>EUSEBIO CAURINO PEÑA</t>
+          <t>FLOR VALDIVIA MILLA</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E140" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G140" s="10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I140" s="11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>CLEMENTE CANTO PATALA</t>
+          <t>EUSEBIO CAURINO PEÑA</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E141" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I141" s="11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142">
@@ -29856,98 +29993,92 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>MARIA MARTINA PEÑA VEGA</t>
+          <t>CLEMENTE CANTO PATALA</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E142" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G142" s="10" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I142" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>JESSICA OLIVO INGARUCA</t>
+          <t>MARIA MARTINA PEÑA VEGA</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E143" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I143" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>VANESSA MILLA CRUZ</t>
+          <t>JESSICA OLIVO INGARUCA</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
@@ -29973,72 +30104,72 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>LUIS ROMERO QUISPE</t>
+          <t>VANESSA MILLA CRUZ</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G145" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I145" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>PEDRO CANDACHO HUARAC</t>
+          <t>LUIS ROMERO QUISPE</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F146" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I146" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -30049,12 +30180,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>ROBERTO PALMADERA MILLA</t>
+          <t>PEDRO CANDACHO HUARAC</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -30066,14 +30197,20 @@
       <c r="F147" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G147" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I147" s="11" t="n">
-        <v>0</v>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -30084,63 +30221,57 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>MIGUEL MELENDEZ JULCA</t>
+          <t>ROBERTO PALMADERA MILLA</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F148" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H148" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I148" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>YESICA ESPINOZA FERNANDEZ</t>
+          <t>MIGUEL MELENDEZ JULCA</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
@@ -30166,22 +30297,22 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>JULIO CHAVARRIA GARCIA</t>
+          <t>YESICA ESPINOZA FERNANDEZ</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F150" s="8" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
@@ -30207,22 +30338,22 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>VICKI MASIAS CUSIHUAMAN</t>
+          <t>JULIO CHAVARRIA GARCIA</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
@@ -30248,22 +30379,22 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>RENATO ALBORNOS SIGUEÑAS</t>
+          <t>VICKI MASIAS CUSIHUAMAN</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F152" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
@@ -30289,22 +30420,22 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>LUZ MERCEDES VARGAS CAURINO</t>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
@@ -30325,41 +30456,82 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>LUZ MERCEDES VARGAS CAURINO</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
         <is>
           <t>DIEGO MAYO SAMARITANO</t>
         </is>
       </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G154" s="10" t="n">
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="H154" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I154" s="11" t="n">
+      <c r="H155" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I155" s="11" t="n">
         <v>50</v>
       </c>
     </row>
@@ -30710,10 +30882,10 @@
         <v>25</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -30945,10 +31117,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -31133,10 +31305,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -31791,10 +31963,10 @@
         <v>25</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -32120,10 +32292,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>-16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
@@ -33204,7 +33376,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -33953,10 +34125,10 @@
         <v>25</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -34517,10 +34689,10 @@
         <v>25</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M88" s="11" t="n">
-        <v>-30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -34893,10 +35065,10 @@
         <v>25</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M96" s="11" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -34940,10 +35112,10 @@
         <v>25</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M97" s="11" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98">
@@ -37102,10 +37274,10 @@
         <v>25</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M143" s="11" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
     </row>
     <row r="144">

--- a/shared/vista_seguimiento_pueblo.xlsx
+++ b/shared/vista_seguimiento_pueblo.xlsx
@@ -24556,14 +24556,20 @@
       <c r="F4" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G4" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0</v>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -30741,10 +30747,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
